--- a/pensum/ol19/OL19_Organisasjonskultur_Oppgaver_v6.xlsx
+++ b/pensum/ol19/OL19_Organisasjonskultur_Oppgaver_v6.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="168">
   <si>
     <t xml:space="preserve">Organisasjonskultur: oppgaver til kapittel 19</t>
   </si>
@@ -65,22 +65,46 @@
     <t xml:space="preserve">Dette er øvingsmateriell til repetisjons- og øvingsstøtte. I besvarelser, caser, prosjektoppgaver og eksamen gjelder lærebøkene og oppgitte primærkilder.</t>
   </si>
   <si>
+    <t xml:space="preserve">Strukturen: avdelingene har ulike rutiner for avvik</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1A: Hvem melder sin egen feil? Kulturen hos Nordlys i tall og begreper</t>
   </si>
   <si>
+    <t xml:space="preserve">Kulturen: ulike uformelle normer for hva som skjer med den som sier fra</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alene, i par eller i gruppe, slik du vil.</t>
   </si>
   <si>
+    <t xml:space="preserve">Kompetansen: montørene i prosjekt er dårligere fagfolk</t>
+  </si>
+  <si>
     <t xml:space="preserve">Situasjonen</t>
   </si>
   <si>
+    <t xml:space="preserve">Verdi</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nordlys Elektro AS meldte 32 avvik i fjor. Alle avdelingene har samme avviksskjema, samme perm for helse, miljø og sikkerhet og samme daglige leder. Likevel meldte solcelle og lading 5 av 6 egne feil, service 11 av 17 og prosjekt og nybygg 2 av 9. På et nybygg la en montør om en kursfordeling fordi skapet var for lite, uten å rette kursfortegnelsen. Feilen ble funnet ved sluttkontrollen 11 uker senere, og omgjøringen tok 2 montører 2 dager à 8 timer. Timeprisen Nordlys tar av kunden er 890 kr uten merverdiavgift (faktaarket). Montøren sier: «Jeg tenkte det ordnet seg.» Tom vil gi ham en advarsel og sende ut en påminnelse. Fjell Elektro AS er med i sorteringen: Mona Fjell, eieren, og to montører.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formell norm</t>
+  </si>
+  <si>
     <t xml:space="preserve">Begrepene du trenger</t>
   </si>
   <si>
+    <t xml:space="preserve">Uformell norm</t>
+  </si>
+  <si>
     <t xml:space="preserve">Organisasjonskultur er det sett av verdier, normer og virkelighetsoppfatninger som preger organisasjonen (19.1). Kulturen har stor innvirkning på hvordan de formelle oppgavene løses. En verdi er det som holdes for verdifullt, ønskelig og godt. En norm er en uskreven regel for hva som er akseptabel atferd; brudd fører ofte til sanksjoner. Formelle normer er regler, rutiner og prosedyrer; uformelle normer er skikk og bruk. Virkelighetsoppfatninger er det Edgar Schein kaller grunnleggende antagelser: det som tas for gitt som sant. Kulturelle symboler, artefakter, er det håndfaste uttrykket for kulturen (19.2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virkelighetsoppfatning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kulturelt symbol</t>
   </si>
   <si>
     <t xml:space="preserve">Tallene</t>
@@ -189,7 +213,16 @@
     <t xml:space="preserve">Gule celler fyller du inn. Grønne regnes ut av arket. Sjekken til høyre forteller om svaret stemmer, og hva du bør se på hvis ikke.</t>
   </si>
   <si>
+    <t xml:space="preserve">Nasjonal og lokal kultur</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1B: Fjell Elektro: hvor kommer kulturen fra, og hva styrer Mona?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ledelsens kulturbygging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Markedet</t>
   </si>
   <si>
     <t xml:space="preserve">Fjell Elektro AS er i dag Mona Fjell og to montører. Etter sommeren begynner en lærling og en tredje montør, som kommer fra en større installasjonsbedrift. Jobbene fordeles over kaffen hver morgen. Kundene er boligeiere og små næringskunder i Oslo øst, og de sier fra samme dag hvis de ikke er fornøyde. Sjekklista før spenningssetting finnes, men den ene montøren tar den «når vi har tid». Mona vil la lærlingen gå med montørene fra dag én.</t>
@@ -237,21 +270,45 @@
     <t xml:space="preserve">Morgenkaffen der jobbene fordeles: hva er det i kapitlets språk?</t>
   </si>
   <si>
+    <t xml:space="preserve">En formell norm, som en stillingsinstruks</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mona vil la lærlingen gå med montørene fra dag én, uten noe program. Hva sier boka?</t>
   </si>
   <si>
+    <t xml:space="preserve">En daglig rite, som ledelsen kan utforme og bruke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En subkultur blant montørene</t>
+  </si>
+  <si>
     <t xml:space="preserve">a) Hvor stor del av Fjell er ny etter sommeren? 2 nye av 5 personer, i prosent med én desimal</t>
   </si>
   <si>
+    <t xml:space="preserve">Greit: kulturen læres uansett</t>
+  </si>
+  <si>
     <t xml:space="preserve">b) Hvor stor del av Nordlys er ny i et år med 2 nye av 18 ansatte? I prosent med én desimal</t>
   </si>
   <si>
+    <t xml:space="preserve">Et systematisk opplæringsprogram er også en introduksjon til verdigrunnlaget, ikke bare til oppgavene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bare et innvielsesritual gir vellykket sosialisering</t>
+  </si>
+  <si>
     <t xml:space="preserve">c) Hva bør Mona gjøre de første ukene etter sommeren, så lærlingen og den nye montøren lærer sjekklista som den riktige måten? Bruk minst to av virkemidlene fra kapitlet, og ordene sjekkliste og morgen. Tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ja, en av de tre</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1C: To avdelinger som én, og Monas sterke kultur: subkultur, motkultur og gruppetenkning</t>
   </si>
   <si>
+    <t xml:space="preserve">Nei</t>
+  </si>
+  <si>
     <t xml:space="preserve">Før Kari lyste ut stillingen som avdelingsleder for solcelle og lading, vurderte hun å legge de to solcellemontørene inn under Tom i service. Service har 4 montører og 1 lærling og meldte 17 avvik i fjor, 11 av dem av den som gjorde feilen. Solcelle og lading meldte 6, 5 av dem selv. Servicemontørene sier: «Kunden skal være fornøyd før du kjører.» De to på solcelle sier: «Vi finner ut av det sammen.» Tom sier: «De gjør det på sin egen måte. Det er en motkultur.» Hos Fjell sier Mona: «Vi tre er alltid enige, og vi har aldri meldt et avvik. Vi har en sterk kultur.»</t>
   </si>
   <si>
@@ -267,7 +324,13 @@
     <t xml:space="preserve">Folk</t>
   </si>
   <si>
+    <t xml:space="preserve">Kulturell styrke</t>
+  </si>
+  <si>
     <t xml:space="preserve">Service (Tom): 4 montører og 1 lærling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kulturell kongruens</t>
   </si>
   <si>
     <t xml:space="preserve">Solcelle og lading: 2 montører, ingen leder</t>
@@ -286,16 +349,34 @@
     <t xml:space="preserve">a) Andel av avvikene i den nye avdelingen som ville vært meldt av den som gjorde feilen: (11 + 5) av (17 + 6), i prosent med én desimal</t>
   </si>
   <si>
+    <t xml:space="preserve">Ja: alt som avviker fra flertallet i avdelingen, er motkultur</t>
+  </si>
+  <si>
     <t xml:space="preserve">b) Hvor stor del av de 7 i den nye avdelingen kommer fra solcelle og lading? I prosent med én desimal</t>
   </si>
   <si>
+    <t xml:space="preserve">Ja: når kongruensen blir lav, er det per definisjon motkultur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nei: en subkultur blir motkultur først når den står for noe vesentlig annet på viktige områder</t>
+  </si>
+  <si>
     <t xml:space="preserve">c) Er dette en av de tre måtene organisasjonsstrukturen skaper subkulturer på (19.4)? (velg i nedtrekksmenyen)</t>
   </si>
   <si>
+    <t xml:space="preserve">Hun har rett: enighet og null avvik er tegn på en sterk og god kultur</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 Solcellemontørene ser bare egne anlegg og lite av servicejobbene</t>
   </si>
   <si>
+    <t xml:space="preserve">Rask enighet og null avvik kan være gruppetenkning: konsensus framfor alt, og ingen tester ideene</t>
+  </si>
+  <si>
     <t xml:space="preserve">2 Service snakker om kunder og kjøretid, solcelle om vekselrettere og produksjon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fjell er for liten til å ha en kultur, så utsagnet er meningsløst</t>
   </si>
   <si>
     <t xml:space="preserve">3 Hver avdeling legger bare merke til informasjon som er nyttig for seg</t>
@@ -644,7 +725,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -667,6 +748,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1113,7 +1198,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G49"/>
+  <dimension ref="B1:Z63"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1121,425 +1206,659 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="Z4" s="6" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="Z5" s="6" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="Z6" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="Z7" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="Z9" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="Z10" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z11" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z12" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+      <c r="D13" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z13" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z14" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="13" t="n">
+      <c r="B15" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="14" t="n">
         <f aca="false">C12+C13+C14</f>
         <v>32</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="14" t="n">
         <f aca="false">D12+D13+D14</f>
         <v>18</v>
       </c>
+      <c r="Z15" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z16" s="0" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
+      <c r="B17" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="Z17" s="6" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
+      <c r="B18" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="Z18" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z19" s="0" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="G20" s="17" t="str">
+      <c r="B20" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="18" t="str">
         <f aca="false">IF(C20="","Skriv svaret i den gule cellen.",IF(ABS(C20-(ROUND((32-18)/32*100,1)))&lt;=0.1,"Riktig.",IF(ABS(C20-(ROUND(18/32*100,1)))&lt;=0.1,"Du har regnet andelen som meldte sin egen feil. Oppgaven spør om resten: de som ble meldt av andre, 32 − 18.",IF(ABS(C20-(32-18))&lt;=0.1,"Det er antallet, 14. Oppgaven spør om prosent av 32: 14 / 32 × 100.",IF(ABS(C20-(ROUND(14/18*100,1)))&lt;=0.1,"Du har delt på 18. Del på alle avvikene, 32.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z20" s="6" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="G21" s="17" t="str">
+      <c r="B21" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" s="18" t="str">
         <f aca="false">IF(C21="","Skriv svaret i den gule cellen.",IF(ABS(C21-(ROUND(2/9*100,1)))&lt;=0.1,"Riktig.",IF(ABS(C21-(ROUND(7/9*100,1)))&lt;=0.1,"Det er andelen meldt av andre i prosjekt. Oppgaven spør om egne: 2 av 9.",IF(ABS(C21-(ROUND(2/32*100,1)))&lt;=0.1,"Du har delt på alle 32 avvikene. Her er det bare prosjekt og nybygg: 2 av 9.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z21" s="6" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="G22" s="17" t="str">
+      <c r="B22" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="19"/>
+      <c r="D22" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" s="18" t="str">
         <f aca="false">IF(C22="","Skriv svaret i den gule cellen.",IF(C22=(2*2*8*890),"Riktig.",IF(ABS(C22-(2*8*890))&lt;=0,"Du har regnet én montør. Det var to, i to dager hver.",IF(ABS(C22-(2*2*8))&lt;=0,"Det er timene, 32. Gang med timeprisen 890 kr.",IF(ABS(C22-(2*2*890))&lt;=0,"Du har glemt timene per dag. 2 montører × 2 dager × 8 timer = 32 timer.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z22" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z23" s="0" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="19"/>
-      <c r="G24" s="17" t="str">
+      <c r="B24" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="20"/>
+      <c r="G24" s="18" t="str">
         <f aca="false">IF(C24="","Velg i nedtrekksmenyen.",IF(C24="Kulturen: ulike uformelle normer for hva som skjer med den som sier fra","Riktig. Strukturen og de formelle normene er like i alle avdelingene (19.1). Det som skiller, er de uformelle prosessene, som boka knytter til kulturen: kulturen har stor innvirkning på hvordan de formelle oppgavene løses. Montøren var like dyktig dagen han la om kursene som dagen feilen ble funnet.","Ikke riktig. Strukturen og de formelle normene er like i alle avdelingene (19.1). Det som skiller, er de uformelle prosessene, som boka knytter til kulturen: kulturen har stor innvirkning på hvordan de formelle oppgavene løses. Montøren var like dyktig dagen han la om kursene som dagen feilen ble funnet."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z24" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z25" s="0" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
+      <c r="B26" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="Z26" s="6" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
+      <c r="B27" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="Z27" s="6" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="G28" s="17" t="str">
+      <c r="B28" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="20"/>
+      <c r="G28" s="18" t="str">
         <f aca="false">IF(C28="","Velg i nedtrekksmenyen.",IF(C28="Verdi","Riktig. En verdi: det bedriften sier er godt (19.1). Én ting er å vite hva som er godt, noe annet er å gjøre det.","Ikke riktig. En verdi: det bedriften sier er godt (19.1). Én ting er å vite hva som er godt, noe annet er å gjøre det."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z28" s="6" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="19"/>
-      <c r="G29" s="17" t="str">
+      <c r="B29" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="20"/>
+      <c r="G29" s="18" t="str">
         <f aca="false">IF(C29="","Velg i nedtrekksmenyen.",IF(C29="Uformell norm","Riktig. En uformell norm: ingen har skrevet den ned, men den styrer hva som er akseptabelt (19.1).","Ikke riktig. En uformell norm: ingen har skrevet den ned, men den styrer hva som er akseptabelt (19.1)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z29" s="6" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="19"/>
-      <c r="G30" s="17" t="str">
+      <c r="B30" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="20"/>
+      <c r="G30" s="18" t="str">
         <f aca="false">IF(C30="","Velg i nedtrekksmenyen.",IF(C30="Formell norm","Riktig. En formell norm: boka regner regler, rutiner og prosedyrer som formelle normer (19.1).","Ikke riktig. En formell norm: boka regner regler, rutiner og prosedyrer som formelle normer (19.1)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z30" s="6" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C31" s="19"/>
-      <c r="G31" s="17" t="str">
+      <c r="B31" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="20"/>
+      <c r="G31" s="18" t="str">
         <f aca="false">IF(C31="","Velg i nedtrekksmenyen.",IF(C31="Uformell norm","Riktig. En uformell norm, skikk og bruk. Bryter du den, får du høre det: sanksjon (19.1).","Ikke riktig. En uformell norm, skikk og bruk. Bryter du den, får du høre det: sanksjon (19.1)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z31" s="6" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C32" s="19"/>
-      <c r="G32" s="17" t="str">
+      <c r="B32" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="20"/>
+      <c r="G32" s="18" t="str">
         <f aca="false">IF(C32="","Velg i nedtrekksmenyen.",IF(C32="Kulturelt symbol","Riktig. Et kulturelt symbol: logo og påkledning er bokas egne eksempler (19.2).","Ikke riktig. Et kulturelt symbol: logo og påkledning er bokas egne eksempler (19.2)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z32" s="6" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="19"/>
-      <c r="G33" s="17" t="str">
+      <c r="B33" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" s="20"/>
+      <c r="G33" s="18" t="str">
         <f aca="false">IF(C33="","Velg i nedtrekksmenyen.",IF(C33="Virkelighetsoppfatning","Riktig. En virkelighetsoppfatning: noe som tas for gitt som sant uten å bli sagt (19.1). Den forklarer 2 av 9.","Ikke riktig. En virkelighetsoppfatning: noe som tas for gitt som sant uten å bli sagt (19.1). Den forklarer 2 av 9."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z33" s="6" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" s="19"/>
-      <c r="G34" s="17" t="str">
+      <c r="B34" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="20"/>
+      <c r="G34" s="18" t="str">
         <f aca="false">IF(C34="","Velg i nedtrekksmenyen.",IF(C34="Formell norm","Riktig. En formell norm: en skrevet rutine (19.1).","Ikke riktig. En formell norm: en skrevet rutine (19.1)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z34" s="6" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C35" s="19"/>
-      <c r="G35" s="17" t="str">
+      <c r="B35" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="20"/>
+      <c r="G35" s="18" t="str">
         <f aca="false">IF(C35="","Velg i nedtrekksmenyen.",IF(C35="Uformell norm","Riktig. En uformell norm som går foran den formelle. Når de to kolliderer, viser den uformelle hva som faktisk gjelder (19.1).","Ikke riktig. En uformell norm som går foran den formelle. Når de to kolliderer, viser den uformelle hva som faktisk gjelder (19.1)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z35" s="6" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" s="19"/>
-      <c r="G36" s="17" t="str">
+      <c r="B36" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="20"/>
+      <c r="G36" s="18" t="str">
         <f aca="false">IF(C36="","Velg i nedtrekksmenyen.",IF(C36="Verdi","Riktig. En verdi: det Mona sier er godt (19.1). Normen i 8 viser hva som faktisk gjelder.","Ikke riktig. En verdi: det Mona sier er godt (19.1). Normen i 8 viser hva som faktisk gjelder."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z36" s="6" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C37" s="19"/>
-      <c r="G37" s="17" t="str">
+      <c r="B37" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" s="20"/>
+      <c r="G37" s="18" t="str">
         <f aca="false">IF(C37="","Velg i nedtrekksmenyen.",IF(C37="Virkelighetsoppfatning","Riktig. En virkelighetsoppfatning: hvordan Mona tar for gitt at hennes bedrift er (19.1). Den kan forklare hvorfor sjekklista hoppes over.","Ikke riktig. En virkelighetsoppfatning: hvordan Mona tar for gitt at hennes bedrift er (19.1). Den kan forklare hvorfor sjekklista hoppes over."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z37" s="6" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="C38" s="19"/>
-      <c r="G38" s="17" t="str">
+      <c r="B38" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="20"/>
+      <c r="G38" s="18" t="str">
         <f aca="false">IF(C38="","Velg i nedtrekksmenyen.",IF(C38="Kulturelt symbol","Riktig. Et kulturelt symbol: språk og fagspråk preger kulturen, og tonen smitter over på resten av samtalen (19.2).","Ikke riktig. Et kulturelt symbol: språk og fagspråk preger kulturen, og tonen smitter over på resten av samtalen (19.2)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z38" s="6" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" s="19"/>
-      <c r="G39" s="17" t="str">
+      <c r="B39" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" s="20"/>
+      <c r="G39" s="18" t="str">
         <f aca="false">IF(C39="","Velg i nedtrekksmenyen.",IF(C39="Kulturelt symbol","Riktig. Et kulturelt symbol: historiene er en del av den kulturelle arven (19.2).","Ikke riktig. Et kulturelt symbol: historiene er en del av den kulturelle arven (19.2)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z39" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z40" s="0" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
+      <c r="B41" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="Z41" s="6" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="20"/>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+      <c r="Z42" s="6" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="20"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="Z43" s="6" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="20"/>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
+      <c r="Z44" s="6" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="21" t="str">
+      <c r="B45" s="22" t="str">
         <f aca="false">IF(LEN(B42)&lt;40,"",IF(AND(ISNUMBER(SEARCH("norm",B42)),ISNUMBER(SEARCH("erfar",B42))),"Bra: du bruker både norm og erfaring. Sjekk at du sier hvilken norm påminnelsen ikke rører (den uformelle), og hva Kari kan gjøre som gir ny erfaring: takke den som melder, og melde egne feil selv.",IF(OR(ISNUMBER(SEARCH("norm",B42)),ISNUMBER(SEARCH("erfar",B42))),"Du er på sporet. Si at påminnelsen gjentar den formelle normen som alle kjenner, mens problemet sitter i den uformelle normen, og at kulturen er lært av erfaring og bare endres av ny erfaring.","Tips: påminnelsen gjentar den formelle normen og verdien, som alle kjenner fra før. Advarselen er en sanksjon alle ser, og den bekrefter normen «meld bare hvis noen andre ser det». Schein: kulturen er lært og består så lenge den oppfattes som riktig. Kari må gi ny erfaring: spørre hva som gjorde feilen mulig, takke den som melder, og melde egne feil selv. 28 480 kr er argumentet.")))</f>
         <v/>
       </c>
-      <c r="C45" s="21"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="21"/>
-      <c r="G45" s="21"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="22"/>
+      <c r="Z45" s="6" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="C46" s="19"/>
+      <c r="B46" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46" s="20"/>
+      <c r="Z46" s="6" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="23" t="str">
+      <c r="B47" s="24" t="str">
         <f aca="false">IF(C46="JA","Hint: a: (32 − 18) / 32 × 100 = 43,8. b: 2 / 9 × 100 = 22,2. c: 2 × 2 × 8 = 32 timer, 32 × 890 = 28 480 kr. d: kulturen. e: plakaten og «sikkerhet viktigst» er verdier; permen og sjekklista er formelle normer; «hvis andre ser det», «sist fyller bilen» og «når vi har tid» er uformelle normer; «det koster å innrømme» og «rutiner er for store bedrifter» er virkelighetsoppfatninger; logoen, fagspråket og historien er kulturelle symboler.","")</f>
         <v/>
       </c>
-      <c r="C47" s="23"/>
-      <c r="D47" s="23"/>
-      <c r="E47" s="23"/>
-      <c r="F47" s="23"/>
-      <c r="G47" s="23"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
+      <c r="Z47" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z48" s="0" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
+      <c r="B49" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+      <c r="Z49" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z50" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z51" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z52" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z53" s="0" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z54" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z55" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z56" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z57" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z58" s="0" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z59" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z60" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z61" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z62" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z63" s="0" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -1691,55 +2010,55 @@
   </conditionalFormatting>
   <dataValidations count="14">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C24" type="list">
-      <formula1>"Strukturen: avdelingene har ulike rutiner for avvik,Kulturen: ulike uformelle normer for hva som skjer med den som sier fra,Kompetansen: montørene i prosjekt er dårligere fagfolk"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C28" type="list">
-      <formula1>"Verdi,Formell norm,Uformell norm,Virkelighetsoppfatning,Kulturelt symbol"</formula1>
+      <formula1>$Z$4:$Z$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C29" type="list">
-      <formula1>"Verdi,Formell norm,Uformell norm,Virkelighetsoppfatning,Kulturelt symbol"</formula1>
+      <formula1>$Z$9:$Z$13</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C30" type="list">
-      <formula1>"Verdi,Formell norm,Uformell norm,Virkelighetsoppfatning,Kulturelt symbol"</formula1>
+      <formula1>$Z$14:$Z$18</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C31" type="list">
-      <formula1>"Verdi,Formell norm,Uformell norm,Virkelighetsoppfatning,Kulturelt symbol"</formula1>
+      <formula1>$Z$19:$Z$23</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C32" type="list">
-      <formula1>"Verdi,Formell norm,Uformell norm,Virkelighetsoppfatning,Kulturelt symbol"</formula1>
+      <formula1>$Z$24:$Z$28</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C33" type="list">
-      <formula1>"Verdi,Formell norm,Uformell norm,Virkelighetsoppfatning,Kulturelt symbol"</formula1>
+      <formula1>$Z$29:$Z$33</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C34" type="list">
-      <formula1>"Verdi,Formell norm,Uformell norm,Virkelighetsoppfatning,Kulturelt symbol"</formula1>
+      <formula1>$Z$34:$Z$38</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C35" type="list">
-      <formula1>"Verdi,Formell norm,Uformell norm,Virkelighetsoppfatning,Kulturelt symbol"</formula1>
+      <formula1>$Z$39:$Z$43</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C36" type="list">
-      <formula1>"Verdi,Formell norm,Uformell norm,Virkelighetsoppfatning,Kulturelt symbol"</formula1>
+      <formula1>$Z$44:$Z$48</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C37" type="list">
-      <formula1>"Verdi,Formell norm,Uformell norm,Virkelighetsoppfatning,Kulturelt symbol"</formula1>
+      <formula1>$Z$49:$Z$53</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C38" type="list">
-      <formula1>"Verdi,Formell norm,Uformell norm,Virkelighetsoppfatning,Kulturelt symbol"</formula1>
+      <formula1>$Z$54:$Z$58</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C39" type="list">
-      <formula1>"Verdi,Formell norm,Uformell norm,Virkelighetsoppfatning,Kulturelt symbol"</formula1>
+      <formula1>$Z$59:$Z$63</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C46" type="list">
@@ -1762,7 +2081,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G39"/>
+  <dimension ref="B1:Z39"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1770,315 +2089,420 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>61</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="Z4" s="6" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="Z5" s="6" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="Z6" s="6" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="Z7" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="Z9" s="6" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="Z10" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z11" s="0" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
+      <c r="B12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="Z12" s="6" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
+      <c r="B13" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="Z13" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z14" s="0" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
+      <c r="B15" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="Z15" s="6" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="19"/>
-      <c r="G16" s="17" t="str">
+      <c r="B16" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="20"/>
+      <c r="G16" s="18" t="str">
         <f aca="false">IF(C16="","Velg i nedtrekksmenyen.",IF(C16="Nasjonal og lokal kultur","Riktig. Han er ingen tabula rasa, ikke et ubeskrevet blad: utdanning, tidligere jobber og resten av livet har gitt ham verdier og normer han tar med inn (19.3.1).","Ikke riktig. Han er ingen tabula rasa, ikke et ubeskrevet blad: utdanning, tidligere jobber og resten av livet har gitt ham verdier og normer han tar med inn (19.3.1)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z16" s="6" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="19"/>
-      <c r="G17" s="17" t="str">
+      <c r="B17" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="G17" s="18" t="str">
         <f aca="false">IF(C17="","Velg i nedtrekksmenyen.",IF(C17="Markedet","Riktig. Markedet: hvor raskt tilbakemeldingen kommer, former kulturen (19.3.3).","Ikke riktig. Markedet: hvor raskt tilbakemeldingen kommer, former kulturen (19.3.3)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z17" s="6" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="19"/>
-      <c r="G18" s="17" t="str">
+      <c r="B18" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="20"/>
+      <c r="G18" s="18" t="str">
         <f aca="false">IF(C18="","Velg i nedtrekksmenyen.",IF(C18="Ledelsens kulturbygging","Riktig. Sosialisering: velkomst, presentasjon og opplæringsprogram er ledelsens (19.3.2).","Ikke riktig. Sosialisering: velkomst, presentasjon og opplæringsprogram er ledelsens (19.3.2)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z18" s="6" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" s="19"/>
-      <c r="G19" s="17" t="str">
+      <c r="B19" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="20"/>
+      <c r="G19" s="18" t="str">
         <f aca="false">IF(C19="","Velg i nedtrekksmenyen.",IF(C19="Nasjonal og lokal kultur","Riktig. Norsk kultur: nærhet mellom de styrende og de styrte, og lite aksept for store lønnsforskjeller (19.3.1).","Ikke riktig. Norsk kultur: nærhet mellom de styrende og de styrte, og lite aksept for store lønnsforskjeller (19.3.1)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z19" s="6" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="19"/>
-      <c r="G20" s="17" t="str">
+      <c r="B20" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="20"/>
+      <c r="G20" s="18" t="str">
         <f aca="false">IF(C20="","Velg i nedtrekksmenyen.",IF(C20="Ledelsens kulturbygging","Riktig. En daglig rite: hvordan arbeidsdagen starter. Bare ledelsen kan utforme og opprettholde den (19.3.2).","Ikke riktig. En daglig rite: hvordan arbeidsdagen starter. Bare ledelsen kan utforme og opprettholde den (19.3.2)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z20" s="6" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="19"/>
-      <c r="G21" s="17" t="str">
+      <c r="B21" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="20"/>
+      <c r="G21" s="18" t="str">
         <f aca="false">IF(C21="","Velg i nedtrekksmenyen.",IF(C21="Markedet","Riktig. Markedet: konkurranse gir press på lønnsomheten og dermed risiko (19.3.3).","Ikke riktig. Markedet: konkurranse gir press på lønnsomheten og dermed risiko (19.3.3)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z21" s="6" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="19"/>
-      <c r="G22" s="17" t="str">
+      <c r="B22" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="20"/>
+      <c r="G22" s="18" t="str">
         <f aca="false">IF(C22="","Velg i nedtrekksmenyen.",IF(C22="Ledelsens kulturbygging","Riktig. Rekruttering: en vellykket sosialisering starter med en god rekrutteringsprosess (19.3.2).","Ikke riktig. Rekruttering: en vellykket sosialisering starter med en god rekrutteringsprosess (19.3.2)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z22" s="6" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" s="19"/>
-      <c r="G23" s="17" t="str">
+      <c r="B23" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="20"/>
+      <c r="G23" s="18" t="str">
         <f aca="false">IF(C23="","Velg i nedtrekksmenyen.",IF(C23="Nasjonal og lokal kultur","Riktig. Nasjonale verdier som likebehandling og toleranse tas med inn i bedriften (19.3.1).","Ikke riktig. Nasjonale verdier som likebehandling og toleranse tas med inn i bedriften (19.3.1)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z23" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z24" s="0" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" s="19"/>
-      <c r="G25" s="17" t="str">
+      <c r="B25" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="20"/>
+      <c r="G25" s="18" t="str">
         <f aca="false">IF(C25="","Velg i nedtrekksmenyen.",IF(C25="En daglig rite, som ledelsen kan utforme og bruke","Riktig. Boka (19.3.2): de daglige ritene, som hvordan starten på arbeidsdagen markeres og hvordan møter gjennomføres, er prosaiske, men kanskje enda viktigere enn jubileer. Bare ledelsen er i posisjon til å utforme og opprettholde dem.","Ikke riktig. Boka (19.3.2): de daglige ritene, som hvordan starten på arbeidsdagen markeres og hvordan møter gjennomføres, er prosaiske, men kanskje enda viktigere enn jubileer. Bare ledelsen er i posisjon til å utforme og opprettholde dem."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z25" s="6" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="G26" s="17" t="str">
+      <c r="B26" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" s="20"/>
+      <c r="G26" s="18" t="str">
         <f aca="false">IF(C26="","Velg i nedtrekksmenyen.",IF(C26="Et systematisk opplæringsprogram er også en introduksjon til verdigrunnlaget, ikke bare til oppgavene","Riktig. Boka (19.3.2): en varm velkomst og en skikkelig presentasjon gjør nytten av et innvielsesritual, men enda viktigere er et systematisk opplæringsprogram, som også er en introduksjon til bedriftens verdigrunnlag og kultur. Uten program lærer lærlingen det montørene gjør: sjekklista «når vi har tid».","Ikke riktig. Boka (19.3.2): en varm velkomst og en skikkelig presentasjon gjør nytten av et innvielsesritual, men enda viktigere er et systematisk opplæringsprogram, som også er en introduksjon til bedriftens verdigrunnlag og kultur. Uten program lærer lærlingen det montørene gjør: sjekklista «når vi har tid»."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z26" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z27" s="0" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" s="15"/>
-      <c r="D28" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="G28" s="17" t="str">
+      <c r="B28" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" s="16"/>
+      <c r="D28" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G28" s="18" t="str">
         <f aca="false">IF(C28="","Skriv svaret i den gule cellen.",IF(ABS(C28-(ROUND(2/5*100,1)))&lt;=0.1,"Riktig.",IF(ABS(C28-(ROUND(2/3*100,1)))&lt;=0.1,"Du har delt på de tre som er der i dag. Etter sommeren er Fjell 3 + 2 = 5 personer.",IF(ABS(C28-(ROUND(3/5*100,1)))&lt;=0.1,"Det er andelen gamle. Oppgaven spør om de nye: 2 av 5.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z28" s="6" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" s="15"/>
-      <c r="D29" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="G29" s="17" t="str">
+      <c r="B29" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="16"/>
+      <c r="D29" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G29" s="18" t="str">
         <f aca="false">IF(C29="","Skriv svaret i den gule cellen.",IF(ABS(C29-(ROUND(2/18*100,1)))&lt;=0.1,"Riktig.",IF(ABS(C29-(ROUND(2/20*100,1)))&lt;=0.1,"Du har lagt de to til de 18. Forutsetningen er 2 nye av 18 ansatte i alt.",IF(ABS(C29-(ROUND(2/12*100,1)))&lt;=0.1,"Du har delt på montørene. Nordlys har 18 ansatte.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z29" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z30" s="0" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
+      <c r="B31" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="21" t="str">
+      <c r="B35" s="22" t="str">
         <f aca="false">IF(LEN(B32)&lt;40,"",IF(AND(ISNUMBER(SEARCH("sjekklist",B32)),ISNUMBER(SEARCH("morgen",B32))),"Bra: du bruker både sjekklista og morgenmøtet. Sjekk at du også sier noe om den nye montøren: han er ingen tabula rasa, så spør hva de gjorde annerledes der han kom fra.",IF(OR(ISNUMBER(SEARCH("sjekklist",B32)),ISNUMBER(SEARCH("morgen",B32))),"Du er på sporet. Ta med både et opplæringsprogram med sjekklista først, og morgenkaffen som rite der lærlingen spørres først om hva som kan gå galt.","Tips: velkomst og et systematisk opplæringsprogram med sjekklista som det første lærlingen lærer. Bruk morgenkaffen som rite: spør lærlingen først hva som kan gå galt, og takk den som sier fra. Ta sjekklista selv, hver gang, også når det haster. Spør den nye montøren hva de gjorde annerledes der han kom fra.")))</f>
         <v/>
       </c>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="C36" s="19"/>
+      <c r="B36" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="20"/>
     </row>
     <row r="37" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="23" t="str">
+      <c r="B37" s="24" t="str">
         <f aca="false">IF(C36="JA","Hint: Tabula rasa, lønnsforskjeller og likebehandling er den nasjonale og lokale kulturen. Velkomsten, morgenkaffen og ansettelsen er ledelsens kulturbygging. Kundene som sier fra samme dag og prispresset er markedet. a: 2 / 5 × 100 = 40,0. b: 2 / 18 × 100 = 11,1.","")</f>
         <v/>
       </c>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
+      <c r="B39" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -2197,43 +2621,43 @@
   </conditionalFormatting>
   <dataValidations count="11">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C16" type="list">
-      <formula1>"Nasjonal og lokal kultur,Ledelsens kulturbygging,Markedet"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C17" type="list">
-      <formula1>"Nasjonal og lokal kultur,Ledelsens kulturbygging,Markedet"</formula1>
+      <formula1>$Z$4:$Z$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C18" type="list">
-      <formula1>"Nasjonal og lokal kultur,Ledelsens kulturbygging,Markedet"</formula1>
+      <formula1>$Z$7:$Z$9</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C19" type="list">
-      <formula1>"Nasjonal og lokal kultur,Ledelsens kulturbygging,Markedet"</formula1>
+      <formula1>$Z$10:$Z$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C20" type="list">
-      <formula1>"Nasjonal og lokal kultur,Ledelsens kulturbygging,Markedet"</formula1>
+      <formula1>$Z$13:$Z$15</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C21" type="list">
-      <formula1>"Nasjonal og lokal kultur,Ledelsens kulturbygging,Markedet"</formula1>
+      <formula1>$Z$16:$Z$18</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C22" type="list">
-      <formula1>"Nasjonal og lokal kultur,Ledelsens kulturbygging,Markedet"</formula1>
+      <formula1>$Z$19:$Z$21</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C23" type="list">
-      <formula1>"Nasjonal og lokal kultur,Ledelsens kulturbygging,Markedet"</formula1>
+      <formula1>$Z$22:$Z$24</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C25" type="list">
-      <formula1>"En formell norm,som en stillingsinstruks,En daglig rite,som ledelsen kan utforme og bruke,En subkultur blant montørene"</formula1>
+      <formula1>$Z$25:$Z$27</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C26" type="list">
-      <formula1>"Greit: kulturen læres uansett,Et systematisk opplæringsprogram er også en introduksjon til verdigrunnlaget,ikke bare til oppgavene,Bare et innvielsesritual gir vellykket sosialisering"</formula1>
+      <formula1>$Z$28:$Z$30</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C36" type="list">
@@ -2256,7 +2680,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G46"/>
+  <dimension ref="B1:Z46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2264,394 +2688,477 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>89</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="Z4" s="6" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="Z5" s="6" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="Z6" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="Z7" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="Z9" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="Z10" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z11" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="12" t="n">
+      <c r="E12" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z12" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="D12" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>5</v>
+      <c r="Z13" s="6" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" s="13" t="n">
+      <c r="B14" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="14" t="n">
         <f aca="false">C12+C13</f>
         <v>7</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="14" t="n">
         <f aca="false">D12+D13</f>
         <v>23</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="14" t="n">
         <f aca="false">E12+E13</f>
         <v>16</v>
       </c>
+      <c r="Z14" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z15" s="0" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
+      <c r="B16" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="Z16" s="6" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
+      <c r="B17" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="Z17" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z18" s="0" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19" s="17" t="str">
+      <c r="B19" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19" s="18" t="str">
         <f aca="false">IF(C19="","Skriv svaret i den gule cellen.",IF(ABS(C19-(ROUND(16/23*100,1)))&lt;=0.1,"Riktig.",IF(ABS(C19-(ROUND(11/17*100,1)))&lt;=0.1,"Det er service alene, 11 av 17. Legg til solcelle: 16 av 23.",IF(ABS(C19-(ROUND((11/17+5/6)/2*100,1)))&lt;=0.1,"Du har tatt snittet av de to andelene. Slå sammen tallene først: 16 av 23. Service har flere avvik og veier tyngre.",IF(ABS(C19-(16))&lt;=0.1,"Det er antallet egne. Oppgaven spør om prosent av 23.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z19" s="6" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="G20" s="17" t="str">
+      <c r="B20" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="18" t="str">
         <f aca="false">IF(C20="","Skriv svaret i den gule cellen.",IF(ABS(C20-(ROUND(2/7*100,1)))&lt;=0.1,"Riktig.",IF(ABS(C20-(ROUND(2/5*100,1)))&lt;=0.1,"Du har delt på de 5 i service. Den nye avdelingen er 5 + 2 = 7.",IF(ABS(C20-(ROUND(5/7*100,1)))&lt;=0.1,"Det er andelen fra service. Oppgaven spør om de to fra solcelle.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z20" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z21" s="0" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
+      <c r="B22" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="Z22" s="6" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" s="19"/>
-      <c r="G23" s="17" t="str">
+      <c r="B23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="20"/>
+      <c r="G23" s="18" t="str">
         <f aca="false">IF(C23="","Velg i nedtrekksmenyen.",IF(C23="Ja, en av de tre","Riktig. Spesialisering: oppmerksomheten rettes mot egne oppgaver, og strukturen skjermer mot innsyn i andres arbeid (19.4).","Ikke riktig. Spesialisering: oppmerksomheten rettes mot egne oppgaver, og strukturen skjermer mot innsyn i andres arbeid (19.4)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z23" s="6" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" s="19"/>
-      <c r="G24" s="17" t="str">
+      <c r="B24" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C24" s="20"/>
+      <c r="G24" s="18" t="str">
         <f aca="false">IF(C24="","Velg i nedtrekksmenyen.",IF(C24="Ja, en av de tre","Riktig. Kommunikasjon: innholdet og formen er annerledes innad i avdelingen enn over grensene (19.4).","Ikke riktig. Kommunikasjon: innholdet og formen er annerledes innad i avdelingen enn over grensene (19.4)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z24" s="6" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C25" s="19"/>
-      <c r="G25" s="17" t="str">
+      <c r="B25" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" s="20"/>
+      <c r="G25" s="18" t="str">
         <f aca="false">IF(C25="","Velg i nedtrekksmenyen.",IF(C25="Ja, en av de tre","Riktig. Seleksjon av informasjon: styrker delmålene og forsterker subkulturen (19.4).","Ikke riktig. Seleksjon av informasjon: styrker delmålene og forsterker subkulturen (19.4)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="G26" s="17" t="str">
+      <c r="B26" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="C26" s="20"/>
+      <c r="G26" s="18" t="str">
         <f aca="false">IF(C26="","Velg i nedtrekksmenyen.",IF(C26="Nei","Riktig. Det er en felles formell norm, ikke noe som skiller avdelingene.","Ikke riktig. Det er en felles formell norm, ikke noe som skiller avdelingene."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" s="19"/>
-      <c r="G27" s="17" t="str">
+      <c r="B27" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="C27" s="20"/>
+      <c r="G27" s="18" t="str">
         <f aca="false">IF(C27="","Velg i nedtrekksmenyen.",IF(C27="Nei","Riktig. Et felles kulturelt symbol (19.2). Det trekker mot én kultur, ikke flere.","Ikke riktig. Et felles kulturelt symbol (19.2). Det trekker mot én kultur, ikke flere."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
+      <c r="B29" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" s="19"/>
-      <c r="G30" s="17" t="str">
+      <c r="B30" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C30" s="20"/>
+      <c r="G30" s="18" t="str">
         <f aca="false">IF(C30="","Velg i nedtrekksmenyen.",IF(C30="Kulturell styrke","Riktig. Styrke: kulturen har stor innflytelse på beslutninger og atferd (19.4).","Ikke riktig. Styrke: kulturen har stor innflytelse på beslutninger og atferd (19.4)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" s="19"/>
-      <c r="G31" s="17" t="str">
+      <c r="B31" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="C31" s="20"/>
+      <c r="G31" s="18" t="str">
         <f aca="false">IF(C31="","Velg i nedtrekksmenyen.",IF(C31="Kulturell kongruens","Riktig. Kongruens, her lav: kulturen er ikke den samme overalt i bedriften (19.4).","Ikke riktig. Kongruens, her lav: kulturen er ikke den samme overalt i bedriften (19.4)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" s="19"/>
-      <c r="G32" s="17" t="str">
+      <c r="B32" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="C32" s="20"/>
+      <c r="G32" s="18" t="str">
         <f aca="false">IF(C32="","Velg i nedtrekksmenyen.",IF(C32="Kulturell kongruens","Riktig. Kongruens, her høy: en enhetlig kultur (19.4).","Ikke riktig. Kongruens, her høy: en enhetlig kultur (19.4)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C33" s="19"/>
-      <c r="G33" s="17" t="str">
+      <c r="B33" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C33" s="20"/>
+      <c r="G33" s="18" t="str">
         <f aca="false">IF(C33="","Velg i nedtrekksmenyen.",IF(C33="Kulturell styrke","Riktig. Styrke: kulturen preger atferden i stor grad, selv om den bare gjelder to personer (19.4).","Ikke riktig. Styrke: kulturen preger atferden i stor grad, selv om den bare gjelder to personer (19.4)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" s="19"/>
-      <c r="G35" s="17" t="str">
+      <c r="B35" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" s="20"/>
+      <c r="G35" s="18" t="str">
         <f aca="false">IF(C35="","Velg i nedtrekksmenyen.",IF(C35="Nei: en subkultur blir motkultur først når den står for noe vesentlig annet på viktige områder","Riktig. Boka (19.4): fravær av enhetskultur er i utgangspunktet ikke et problem, og subkulturer kan forsterke verdiene ledelsen ønsker. De to melder 5 av 6 egne feil; de står for det Nordlys sier at det vil, bare tydeligere.","Ikke riktig. Boka (19.4): fravær av enhetskultur er i utgangspunktet ikke et problem, og subkulturer kan forsterke verdiene ledelsen ønsker. De to melder 5 av 6 egne feil; de står for det Nordlys sier at det vil, bare tydeligere."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="C36" s="19"/>
-      <c r="G36" s="17" t="str">
+      <c r="B36" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" s="20"/>
+      <c r="G36" s="18" t="str">
         <f aca="false">IF(C36="","Velg i nedtrekksmenyen.",IF(C36="Rask enighet og null avvik kan være gruppetenkning: konsensus framfor alt, og ingen tester ideene","Riktig. Boka (19.5): gruppetenkning setter konsensus framfor alt og unngår konflikt nesten for enhver pris, og den utvikler seg lettest i sterke kulturer. Deltagerne er sjelden klar over det mens det skjer. Null avvik på et elektroanlegg betyr ikke null feil.","Ikke riktig. Boka (19.5): gruppetenkning setter konsensus framfor alt og unngår konflikt nesten for enhver pris, og den utvikler seg lettest i sterke kulturer. Deltagerne er sjelden klar over det mens det skjer. Null avvik på et elektroanlegg betyr ikke null feil."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
+      <c r="B38" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="20"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="20"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="20"/>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="21" t="str">
+      <c r="B42" s="22" t="str">
         <f aca="false">IF(LEN(B39)&lt;40,"",IF(AND(ISNUMBER(SEARCH("morgenmøte",B39)),ISNUMBER(SEARCH("avvik",B39))),"Bra: du bruker morgenmøtet som rite og avvikene som tema der. Sjekk at tallet står: de to er 28,6 % av avdelingen, så uten bevisst ledelse lærer de servicenormen, ikke omvendt.",IF(OR(ISNUMBER(SEARCH("morgenmøte",B39)),ISNUMBER(SEARCH("avvik",B39))),"Du er på sporet. Ta med at Tom bruker morgenmøtet til å ta opp avvik, også egne, og takke den som melder, og at de to fra solcelle bare er 28,6 % av avdelingen.","Tips: de to blir 28,6 % av en avdeling med etablerte normer, og uten bevisst ledelse lærer mindretallet flertallets normer. Tom bruker morgenmøtet som daglig rite: avvik, også egne, tas opp der, og den som melder, takkes. La de to vise servicemontørene hvordan de går gjennom en feil sammen. Mål andelen egne avvik etter et år: 69,6 % er et rimelig mål, 64,7 % betyr at solcellekulturen er borte.")))</f>
         <v/>
       </c>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="21"/>
-      <c r="G42" s="21"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="C43" s="19"/>
+      <c r="B43" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C43" s="20"/>
     </row>
     <row r="44" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="23" t="str">
+      <c r="B44" s="24" t="str">
         <f aca="false">IF(C43="JA","Hint: a: (11 + 5) / (17 + 6) × 100 = 16 / 23 × 100 = 69,6. b: 2 / 7 × 100 = 28,6. c: spesialisering, kommunikasjon og seleksjon av informasjon er bokas tre; permen og logoen er felles. d: det som styrer atferden, er styrke; om det er likt overalt, er kongruens. e: subkultur, ikke motkultur. f: gruppetenkning.","")</f>
         <v/>
       </c>
-      <c r="C44" s="23"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="23"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="24"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="24"/>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
+      <c r="B46" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -2779,47 +3286,47 @@
   </conditionalFormatting>
   <dataValidations count="12">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C23" type="list">
-      <formula1>"Ja,en av de tre,Nei"</formula1>
+      <formula1>$Z$1:$Z$2</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C24" type="list">
-      <formula1>"Ja,en av de tre,Nei"</formula1>
+      <formula1>$Z$3:$Z$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C25" type="list">
-      <formula1>"Ja,en av de tre,Nei"</formula1>
+      <formula1>$Z$5:$Z$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C26" type="list">
-      <formula1>"Ja,en av de tre,Nei"</formula1>
+      <formula1>$Z$7:$Z$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C27" type="list">
-      <formula1>"Ja,en av de tre,Nei"</formula1>
+      <formula1>$Z$9:$Z$10</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C30" type="list">
-      <formula1>"Kulturell styrke,Kulturell kongruens"</formula1>
+      <formula1>$Z$11:$Z$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C31" type="list">
-      <formula1>"Kulturell styrke,Kulturell kongruens"</formula1>
+      <formula1>$Z$13:$Z$14</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C32" type="list">
-      <formula1>"Kulturell styrke,Kulturell kongruens"</formula1>
+      <formula1>$Z$15:$Z$16</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C33" type="list">
-      <formula1>"Kulturell styrke,Kulturell kongruens"</formula1>
+      <formula1>$Z$17:$Z$18</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C35" type="list">
-      <formula1>"Ja: alt som avviker fra flertallet i avdelingen,er motkultur,Ja: når kongruensen blir lav,er det per definisjon motkultur,Nei: en subkultur blir motkultur først når den står for noe vesentlig annet på viktige områder"</formula1>
+      <formula1>$Z$19:$Z$21</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C36" type="list">
-      <formula1>"Hun har rett: enighet og null avvik er tegn på en sterk og god kultur,Rask enighet og null avvik kan være gruppetenkning: konsensus framfor alt,og ingen tester ideene,Fjell er for liten til å ha en kultur,så utsagnet er meningsløst"</formula1>
+      <formula1>$Z$22:$Z$24</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C43" type="list">
@@ -2852,199 +3359,199 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="25" t="s">
-        <v>98</v>
+      <c r="B2" s="26" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>102</v>
+      <c r="B5" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="27" t="s">
-        <v>104</v>
+      <c r="B6" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="28" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="27" t="s">
-        <v>106</v>
+      <c r="B7" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="28" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" s="13" t="n">
+      <c r="B8" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" s="14" t="n">
         <v>28480</v>
       </c>
-      <c r="D8" s="27" t="s">
-        <v>108</v>
+      <c r="D8" s="28" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="27" t="s">
-        <v>110</v>
+      <c r="B9" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="28" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="27" t="s">
-        <v>112</v>
+      <c r="B10" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="28" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="27" t="s">
-        <v>114</v>
+      <c r="B11" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="28" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="27" t="s">
-        <v>116</v>
+      <c r="B12" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="28" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="27" t="s">
-        <v>117</v>
-      </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="27" t="s">
-        <v>118</v>
+      <c r="B13" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="28" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="27" t="s">
-        <v>120</v>
+      <c r="B14" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="28" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="27" t="s">
-        <v>122</v>
+      <c r="B15" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="28" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="27" t="s">
-        <v>124</v>
+      <c r="B16" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="C16" s="14"/>
+      <c r="D16" s="28" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="27" t="s">
-        <v>126</v>
+      <c r="B17" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" s="28" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="27" t="s">
-        <v>128</v>
+      <c r="B18" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" s="28" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="27" t="s">
-        <v>129</v>
-      </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="27" t="s">
-        <v>130</v>
+      <c r="B19" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="28" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="27" t="s">
-        <v>132</v>
+      <c r="B20" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="28" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="C21" s="13"/>
-      <c r="D21" s="27" t="s">
-        <v>134</v>
+      <c r="B21" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="C21" s="14"/>
+      <c r="D21" s="28" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="27" t="s">
-        <v>136</v>
+      <c r="B22" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="D22" s="28" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="27" t="s">
-        <v>138</v>
+      <c r="B23" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="C23" s="14"/>
+      <c r="D23" s="28" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="27" t="s">
-        <v>140</v>
+      <c r="B24" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="C24" s="14"/>
+      <c r="D24" s="28" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/pensum/ol19/OL19_Organisasjonskultur_Oppgaver_v6.xlsx
+++ b/pensum/ol19/OL19_Organisasjonskultur_Oppgaver_v6.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Verdi</t>
   </si>
   <si>
-    <t xml:space="preserve">Nordlys Elektro AS meldte 32 avvik i fjor. Alle avdelingene har samme avviksskjema, samme perm for helse, miljø og sikkerhet og samme daglige leder. Likevel meldte solcelle og lading 5 av 6 egne feil, service 11 av 17 og prosjekt og nybygg 2 av 9. På et nybygg la en montør om en kursfordeling fordi skapet var for lite, uten å rette kursfortegnelsen. Feilen ble funnet ved sluttkontrollen 11 uker senere, og omgjøringen tok 2 montører 2 dager à 8 timer. Timeprisen Nordlys tar av kunden er 890 kr uten merverdiavgift (faktaarket). Montøren sier: «Jeg tenkte det ordnet seg.» Tom vil gi ham en advarsel og sende ut en påminnelse. Fjell Elektro AS er med i sorteringen: Mona Fjell, eieren, og to montører.</t>
+    <t xml:space="preserve">Nordlys Elektro AS meldte 32 avvik i fjor. Alle avdelingene har samme avviksskjema, samme perm for helse, miljø og sikkerhet og samme daglige leder. Likevel meldte solcelle og lading 5 av 6 egne feil, service 11 av 17 og prosjekt og nybygg 2 av 9. På et nybygg var underfordelingen levert med for få moduler. En montør satte tre kurser på andre vern enn tegningen viste, uten å rette kursfortegnelsen og uten å melde det. Feilen ble funnet ved sluttkontrollen 11 uker senere. Fordelingen måtte gjøres spenningsløs for omkoblingen, så ny merking, ny kursfortegnelse og ny måling: omgjøringen tok 2 montører 2 dager à 7,5 timer. Kalenderen var full de ukene, så timene kunne ellers vært fakturert på andre jobber. Timeprisen Nordlys tar av kunden er 890 kr uten merverdiavgift (faktaarket). Montørene er fast ansatt og får lønn uansett, så det feilen koster, er faktureringen som gikk tapt. Montøren sier: «Jeg tenkte det ordnet seg.» Tom vil gi ham en advarsel og sende ut en påminnelse. Fjell Elektro AS er med i sorteringen: Mona Fjell, eieren, og to montører.</t>
   </si>
   <si>
     <t xml:space="preserve">Formell norm</t>
@@ -138,7 +138,7 @@
   </si>
   <si>
     <t xml:space="preserve">1. Regn andelen av alle avvikene som ble meldt av noen andre enn den som gjorde feilen (a), og andelen egne feil i prosjekt og nybygg (b). Svar i prosent med én desimal, for eksempel 43,8.
-2. Regn hva feilen ingen meldte, kostet i timer som ikke kunne faktureres (c).
+2. Regn hva feilen ingen meldte, kostet i tapt fakturering (c). Kalenderen var full, så timene kunne ellers vært fakturert på andre jobber.
 3. Velg hva som best forklarer forskjellen mellom avdelingene (d).
 4. Sorter de tolv utsagnene fra Nordlys og Fjell Elektro i kapitlets begreper (e).
 5. Skriv til Kari om Toms to tiltak (f).</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">b) Andel egne feil i prosjekt og nybygg: 2 av 9, i prosent med én desimal</t>
   </si>
   <si>
-    <t xml:space="preserve">c) Omgjøringen av kursfeilen: 2 montører × 2 dager × 8 timer × 890 kr, i hele kroner</t>
+    <t xml:space="preserve">c) Tapt fakturering for omgjøringen av kursfeilen (full kalender): 2 montører × 2 dager × 7,5 timer × 890 kr, i hele kroner</t>
   </si>
   <si>
     <t xml:space="preserve">kr</t>
@@ -225,7 +225,7 @@
     <t xml:space="preserve">Markedet</t>
   </si>
   <si>
-    <t xml:space="preserve">Fjell Elektro AS er i dag Mona Fjell og to montører. Etter sommeren begynner en lærling og en tredje montør, som kommer fra en større installasjonsbedrift. Jobbene fordeles over kaffen hver morgen. Kundene er boligeiere og små næringskunder i Oslo øst, og de sier fra samme dag hvis de ikke er fornøyde. Sjekklista før spenningssetting finnes, men den ene montøren tar den «når vi har tid». Mona vil la lærlingen gå med montørene fra dag én.</t>
+    <t xml:space="preserve">Fjell Elektro AS er i dag Mona Fjell og to montører. Etter sommeren begynner en lærling og en tredje montør, som kommer fra en større installasjonsbedrift. Jobbene fordeles over kaffen hver morgen. Kundene er boligeiere og små næringskunder i Oslo øst, og de sier fra samme dag hvis de ikke er fornøyde. Sjekklista for sluttkontrollen finnes, men den ene montøren tar den «når vi har tid». Lærlingen skal gå med en navngitt montør fra dag én, men Mona har ikke noe opplæringsprogram.</t>
   </si>
   <si>
     <t xml:space="preserve">Organisasjonskultur formes av tre faktorer (19.3): den lokale og nasjonale kulturen, eiernes eller ledelsens bevisste kulturbygging, og markedet. Ingen leder kan kontrollere alle faktorene, men lederen er endringsagent og kontrollerer riter og seremonier, særlig de daglige, sosialiseringen av nye og rekrutteringen (19.3.2). En nyansatt er ikke en tabula rasa, et ubeskrevet blad (19.3.1). Markedet virker gjennom risiko og hvor raskt tilbakemeldingen kommer (19.3.3).</t>
@@ -273,7 +273,7 @@
     <t xml:space="preserve">En formell norm, som en stillingsinstruks</t>
   </si>
   <si>
-    <t xml:space="preserve">Mona vil la lærlingen gå med montørene fra dag én, uten noe program. Hva sier boka?</t>
+    <t xml:space="preserve">Lærlingen skal gå med en navngitt montør fra dag én, som forskriften krever, men uten noe opplæringsprogram. Hva sier boka?</t>
   </si>
   <si>
     <t xml:space="preserve">En daglig rite, som ledelsen kan utforme og bruke</t>
@@ -442,7 +442,7 @@
     <t xml:space="preserve">1A c) Omgjøringen</t>
   </si>
   <si>
-    <t xml:space="preserve">2 × 2 × 8 = 32 timer. 32 × 890 = 28 480 kr som ikke kunne faktureres</t>
+    <t xml:space="preserve">2 × 2 × 7,5 = 30 timer. Full kalender: 30 × 890 = 26 700 kr i tapt fakturering</t>
   </si>
   <si>
     <t xml:space="preserve">1A d) Forklaringen</t>
@@ -1253,7 +1253,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
         <v>20</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="9" t="s">
         <v>37</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>42</v>
       </c>
       <c r="G22" s="18" t="str">
-        <f aca="false">IF(C22="","Skriv svaret i den gule cellen.",IF(C22=(2*2*8*890),"Riktig.",IF(ABS(C22-(2*8*890))&lt;=0,"Du har regnet én montør. Det var to, i to dager hver.",IF(ABS(C22-(2*2*8))&lt;=0,"Det er timene, 32. Gang med timeprisen 890 kr.",IF(ABS(C22-(2*2*890))&lt;=0,"Du har glemt timene per dag. 2 montører × 2 dager × 8 timer = 32 timer.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
+        <f aca="false">IF(C22="","Skriv svaret i den gule cellen.",IF(C22=(2*2*7.5*890),"Riktig.",IF(ABS(C22-(2*7.5*890))&lt;=0,"Du har regnet én montør. Det var to, i to dager hver.",IF(ABS(C22-(2*2*7.5))&lt;=0,"Det er timene, 30. Gang med timeprisen 890 kr.",IF(ABS(C22-(2*2*890))&lt;=0,"Du har glemt timene per dag. 2 montører × 2 dager × 7,5 timer = 30 timer.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
       <c r="Z22" s="6" t="s">
@@ -1737,7 +1737,7 @@
     </row>
     <row r="45" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="22" t="str">
-        <f aca="false">IF(LEN(B42)&lt;40,"",IF(AND(ISNUMBER(SEARCH("norm",B42)),ISNUMBER(SEARCH("erfar",B42))),"Bra: du bruker både norm og erfaring. Sjekk at du sier hvilken norm påminnelsen ikke rører (den uformelle), og hva Kari kan gjøre som gir ny erfaring: takke den som melder, og melde egne feil selv.",IF(OR(ISNUMBER(SEARCH("norm",B42)),ISNUMBER(SEARCH("erfar",B42))),"Du er på sporet. Si at påminnelsen gjentar den formelle normen som alle kjenner, mens problemet sitter i den uformelle normen, og at kulturen er lært av erfaring og bare endres av ny erfaring.","Tips: påminnelsen gjentar den formelle normen og verdien, som alle kjenner fra før. Advarselen er en sanksjon alle ser, og den bekrefter normen «meld bare hvis noen andre ser det». Schein: kulturen er lært og består så lenge den oppfattes som riktig. Kari må gi ny erfaring: spørre hva som gjorde feilen mulig, takke den som melder, og melde egne feil selv. 28 480 kr er argumentet.")))</f>
+        <f aca="false">IF(LEN(B42)&lt;40,"",IF(AND(ISNUMBER(SEARCH("norm",B42)),ISNUMBER(SEARCH("erfar",B42))),"Bra: du bruker både norm og erfaring. Sjekk at du sier hvilken norm påminnelsen ikke rører (den uformelle), og hva Kari kan gjøre som gir ny erfaring: takke den som melder, og melde egne feil selv.",IF(OR(ISNUMBER(SEARCH("norm",B42)),ISNUMBER(SEARCH("erfar",B42))),"Du er på sporet. Si at påminnelsen gjentar den formelle normen som alle kjenner, mens problemet sitter i den uformelle normen, og at kulturen er lært av erfaring og bare endres av ny erfaring.","Tips: påminnelsen gjentar den formelle normen og verdien, som alle kjenner fra før. Advarselen er en sanksjon alle ser, og den bekrefter normen «meld bare hvis noen andre ser det». Schein: kulturen er lært og består så lenge den oppfattes som riktig. Kari må gi ny erfaring: spørre hva som gjorde feilen mulig, takke den som melder, og melde egne feil selv. 26 700 kr er argumentet.")))</f>
         <v/>
       </c>
       <c r="C45" s="22"/>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="47" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="24" t="str">
-        <f aca="false">IF(C46="JA","Hint: a: (32 − 18) / 32 × 100 = 43,8. b: 2 / 9 × 100 = 22,2. c: 2 × 2 × 8 = 32 timer, 32 × 890 = 28 480 kr. d: kulturen. e: plakaten og «sikkerhet viktigst» er verdier; permen og sjekklista er formelle normer; «hvis andre ser det», «sist fyller bilen» og «når vi har tid» er uformelle normer; «det koster å innrømme» og «rutiner er for store bedrifter» er virkelighetsoppfatninger; logoen, fagspråket og historien er kulturelle symboler.","")</f>
+        <f aca="false">IF(C46="JA","Hint: a: (32 − 18) / 32 × 100 = 43,8. b: 2 / 9 × 100 = 22,2. c: 2 × 2 × 7,5 = 30 timer, 30 × 890 = 26 700 kr. d: kulturen. e: plakaten og «sikkerhet viktigst» er verdier; permen og sjekklista er formelle normer; «hvis andre ser det», «sist fyller bilen» og «når vi har tid» er uformelle normer; «det koster å innrømme» og «rutiner er for store bedrifter» er virkelighetsoppfatninger; logoen, fagspråket og historien er kulturelle symboler.","")</f>
         <v/>
       </c>
       <c r="C47" s="24"/>
@@ -2136,7 +2136,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
         <v>65</v>
       </c>
@@ -3404,7 +3404,7 @@
         <v>134</v>
       </c>
       <c r="C8" s="14" t="n">
-        <v>28480</v>
+        <v>26700</v>
       </c>
       <c r="D8" s="28" t="s">
         <v>135</v>

--- a/pensum/ol19/OL19_Organisasjonskultur_Oppgaver_v6.xlsx
+++ b/pensum/ol19/OL19_Organisasjonskultur_Oppgaver_v6.xlsx
@@ -725,7 +725,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -840,6 +840,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1127,7 +1131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1152,27 +1156,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
@@ -1365,8 +1369,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="12" t="s">
+    <row ht="31.5" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="29" r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" s="13" t="n">
@@ -1413,7 +1417,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="90" customHeight="true" r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="9" t="s">
         <v>37</v>
       </c>
@@ -1431,7 +1435,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="20" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="15" t="s">
         <v>38</v>
       </c>
@@ -1463,7 +1467,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="22" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="15" t="s">
         <v>41</v>
       </c>
@@ -1484,7 +1488,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="24" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="15" t="s">
         <v>43</v>
       </c>
@@ -2224,7 +2228,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="60.75" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="9" t="s">
         <v>68</v>
       </c>
@@ -2242,7 +2246,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="25" t="s">
         <v>69</v>
       </c>
@@ -2377,7 +2381,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="26" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="15" t="s">
         <v>80</v>
       </c>
@@ -2894,7 +2898,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="75.75" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="9" t="s">
         <v>102</v>
       </c>
@@ -2912,7 +2916,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="15" t="s">
         <v>103</v>
       </c>
@@ -2928,7 +2932,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="20" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="15" t="s">
         <v>105</v>
       </c>
@@ -2949,7 +2953,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="22" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="25" t="s">
         <v>108</v>
       </c>
@@ -3078,7 +3082,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="36" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="15" t="s">
         <v>123</v>
       </c>
